--- a/entrada/F0009_207/CR-F0009_REV_COMPATIBILIZADA.xlsx
+++ b/entrada/F0009_207/CR-F0009_REV_COMPATIBILIZADA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TECNORED\DADOS\F0009\F0009 - Periféricos - TENAX\0207\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bureauveritas.sharepoint.com/teams/POP-Planejamento/Shared Documents/Automacoes/Comparativo_Cronograma/entrada/F0009_207/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA1E79E-CF3B-446C-937A-6EB8B1989B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DFA1E79E-CF3B-446C-937A-6EB8B1989B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2EF77A9-0260-4B44-A976-6FC14D38A91E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela_Tarefas" sheetId="1" r:id="rId1"/>
@@ -2799,19 +2799,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L712"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="9" max="9" width="26.21875" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7403,7 +7403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7782,7 +7782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8126,7 +8126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -8846,7 +8846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -9190,7 +9190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -9674,7 +9674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -9706,7 +9706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -9741,7 +9741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -9776,7 +9776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -9983,7 +9983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10085,7 +10085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10257,7 +10257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -10601,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -10636,7 +10636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -10706,7 +10706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -11324,7 +11324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -11496,7 +11496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -11668,7 +11668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -11770,7 +11770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -11910,7 +11910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -11977,7 +11977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -12149,7 +12149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -12356,7 +12356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>282</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -12563,7 +12563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>287</v>
       </c>
@@ -12630,7 +12630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -12665,7 +12665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -12700,7 +12700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -12770,7 +12770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>297</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -13044,7 +13044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -13079,7 +13079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -13114,7 +13114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>302</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -13216,7 +13216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -13251,7 +13251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -13286,7 +13286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>307</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>312</v>
       </c>
@@ -13484,7 +13484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>313</v>
       </c>
@@ -13516,7 +13516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -13621,7 +13621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>318</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -13723,7 +13723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -13758,7 +13758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -13828,7 +13828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -13895,7 +13895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -14067,7 +14067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -14137,7 +14137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>333</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -14239,7 +14239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>338</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -14481,7 +14481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>343</v>
       </c>
@@ -14548,7 +14548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -14583,7 +14583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>348</v>
       </c>
@@ -14720,7 +14720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>353</v>
       </c>
@@ -14886,7 +14886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>354</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>359</v>
       </c>
@@ -15090,7 +15090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -15230,7 +15230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -15332,7 +15332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>369</v>
       </c>
@@ -15434,7 +15434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -15539,7 +15539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>374</v>
       </c>
@@ -15606,7 +15606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -15641,7 +15641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -15676,7 +15676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -15711,7 +15711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>379</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -15883,7 +15883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -15918,7 +15918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>384</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -16020,7 +16020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>389</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>394</v>
       </c>
@@ -16288,7 +16288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>395</v>
       </c>
@@ -16320,7 +16320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -16390,7 +16390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -16460,7 +16460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>400</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>405</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -16804,7 +16804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>410</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -16871,7 +16871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -16906,7 +16906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -16976,7 +16976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>415</v>
       </c>
@@ -17008,7 +17008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -17078,7 +17078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>420</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -17215,7 +17215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -17285,7 +17285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>425</v>
       </c>
@@ -17352,7 +17352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -17387,7 +17387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -17422,7 +17422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -17457,7 +17457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>430</v>
       </c>
@@ -17524,7 +17524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -17594,7 +17594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -17629,7 +17629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>435</v>
       </c>
@@ -17696,7 +17696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -17731,7 +17731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -17766,7 +17766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -17836,7 +17836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>440</v>
       </c>
@@ -17868,7 +17868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -17903,7 +17903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -17973,7 +17973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>445</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -18110,7 +18110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -18145,7 +18145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -18180,7 +18180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>450</v>
       </c>
@@ -18212,7 +18212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -18247,7 +18247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -18282,7 +18282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -18317,7 +18317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -18352,7 +18352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>455</v>
       </c>
@@ -18384,7 +18384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -18419,7 +18419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -18454,7 +18454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>460</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -18591,7 +18591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -18661,7 +18661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -18696,7 +18696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>465</v>
       </c>
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -18763,7 +18763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -18833,7 +18833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -18868,7 +18868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>470</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -18935,7 +18935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -18970,7 +18970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -19040,7 +19040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>475</v>
       </c>
@@ -19072,7 +19072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -19177,7 +19177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -19212,7 +19212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A481" s="2">
         <v>480</v>
       </c>
@@ -19238,7 +19238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>481</v>
       </c>
@@ -19270,7 +19270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -19340,7 +19340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -19375,7 +19375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -19410,7 +19410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>486</v>
       </c>
@@ -19442,7 +19442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -19477,7 +19477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -19547,7 +19547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>491</v>
       </c>
@@ -19614,7 +19614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -19649,7 +19649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -19684,7 +19684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -19719,7 +19719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <v>496</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>497</v>
       </c>
@@ -19821,7 +19821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>498</v>
       </c>
@@ -19856,7 +19856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>499</v>
       </c>
@@ -19891,7 +19891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>500</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <v>501</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>502</v>
       </c>
@@ -19993,7 +19993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>503</v>
       </c>
@@ -20028,7 +20028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>504</v>
       </c>
@@ -20063,7 +20063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>505</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <v>506</v>
       </c>
@@ -20130,7 +20130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>507</v>
       </c>
@@ -20165,7 +20165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>508</v>
       </c>
@@ -20200,7 +20200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>509</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>510</v>
       </c>
@@ -20270,7 +20270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <v>511</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>512</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>513</v>
       </c>
@@ -20372,7 +20372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>514</v>
       </c>
@@ -20407,7 +20407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>515</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <v>516</v>
       </c>
@@ -20474,7 +20474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>517</v>
       </c>
@@ -20509,7 +20509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>518</v>
       </c>
@@ -20544,7 +20544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>519</v>
       </c>
@@ -20579,7 +20579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>520</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <v>521</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>522</v>
       </c>
@@ -20681,7 +20681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>523</v>
       </c>
@@ -20716,7 +20716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>524</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>525</v>
       </c>
@@ -20786,7 +20786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <v>526</v>
       </c>
@@ -20818,7 +20818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>527</v>
       </c>
@@ -20853,7 +20853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>528</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>529</v>
       </c>
@@ -20923,7 +20923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>530</v>
       </c>
@@ -20958,7 +20958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <v>531</v>
       </c>
@@ -20990,7 +20990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>532</v>
       </c>
@@ -21025,7 +21025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>533</v>
       </c>
@@ -21060,7 +21060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>534</v>
       </c>
@@ -21095,7 +21095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>535</v>
       </c>
@@ -21130,7 +21130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A537" s="2">
         <v>536</v>
       </c>
@@ -21156,7 +21156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <v>537</v>
       </c>
@@ -21188,7 +21188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>538</v>
       </c>
@@ -21223,7 +21223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>539</v>
       </c>
@@ -21258,7 +21258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>540</v>
       </c>
@@ -21293,7 +21293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>541</v>
       </c>
@@ -21328,7 +21328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
         <v>542</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>543</v>
       </c>
@@ -21395,7 +21395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>544</v>
       </c>
@@ -21430,7 +21430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>545</v>
       </c>
@@ -21465,7 +21465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>546</v>
       </c>
@@ -21500,7 +21500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
         <v>547</v>
       </c>
@@ -21532,7 +21532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>548</v>
       </c>
@@ -21567,7 +21567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>549</v>
       </c>
@@ -21602,7 +21602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>550</v>
       </c>
@@ -21637,7 +21637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>551</v>
       </c>
@@ -21672,7 +21672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
         <v>552</v>
       </c>
@@ -21704,7 +21704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>553</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>554</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>555</v>
       </c>
@@ -21809,7 +21809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>556</v>
       </c>
@@ -21844,7 +21844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
         <v>557</v>
       </c>
@@ -21876,7 +21876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>558</v>
       </c>
@@ -21911,7 +21911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>559</v>
       </c>
@@ -21946,7 +21946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>560</v>
       </c>
@@ -21981,7 +21981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>561</v>
       </c>
@@ -22016,7 +22016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
         <v>562</v>
       </c>
@@ -22048,7 +22048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>563</v>
       </c>
@@ -22083,7 +22083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>564</v>
       </c>
@@ -22118,7 +22118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>565</v>
       </c>
@@ -22153,7 +22153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>566</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
         <v>567</v>
       </c>
@@ -22220,7 +22220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>568</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>569</v>
       </c>
@@ -22290,7 +22290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>570</v>
       </c>
@@ -22325,7 +22325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>571</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
         <v>572</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>573</v>
       </c>
@@ -22427,7 +22427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>574</v>
       </c>
@@ -22462,7 +22462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>575</v>
       </c>
@@ -22497,7 +22497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>576</v>
       </c>
@@ -22532,7 +22532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
         <v>577</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>578</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>579</v>
       </c>
@@ -22634,7 +22634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>580</v>
       </c>
@@ -22669,7 +22669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>581</v>
       </c>
@@ -22704,7 +22704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
         <v>582</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>583</v>
       </c>
@@ -22771,7 +22771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>584</v>
       </c>
@@ -22806,7 +22806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>585</v>
       </c>
@@ -22841,7 +22841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>586</v>
       </c>
@@ -22876,7 +22876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
         <v>587</v>
       </c>
@@ -22908,7 +22908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>588</v>
       </c>
@@ -22943,7 +22943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>589</v>
       </c>
@@ -22978,7 +22978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>590</v>
       </c>
@@ -23013,7 +23013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>591</v>
       </c>
@@ -23048,7 +23048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1">
         <v>592</v>
       </c>
@@ -23080,7 +23080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>593</v>
       </c>
@@ -23115,7 +23115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>594</v>
       </c>
@@ -23150,7 +23150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>595</v>
       </c>
@@ -23185,7 +23185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>596</v>
       </c>
@@ -23220,7 +23220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
         <v>597</v>
       </c>
@@ -23252,7 +23252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>598</v>
       </c>
@@ -23287,7 +23287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>599</v>
       </c>
@@ -23322,7 +23322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>600</v>
       </c>
@@ -23357,7 +23357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>601</v>
       </c>
@@ -23392,7 +23392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
         <v>602</v>
       </c>
@@ -23424,7 +23424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>603</v>
       </c>
@@ -23459,7 +23459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>604</v>
       </c>
@@ -23494,7 +23494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>605</v>
       </c>
@@ -23529,7 +23529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>606</v>
       </c>
@@ -23564,7 +23564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
         <v>607</v>
       </c>
@@ -23596,7 +23596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>608</v>
       </c>
@@ -23631,7 +23631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>609</v>
       </c>
@@ -23666,7 +23666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>610</v>
       </c>
@@ -23701,7 +23701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>611</v>
       </c>
@@ -23736,7 +23736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1">
         <v>612</v>
       </c>
@@ -23768,7 +23768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>613</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>614</v>
       </c>
@@ -23838,7 +23838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>615</v>
       </c>
@@ -23873,7 +23873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>616</v>
       </c>
@@ -23908,7 +23908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1">
         <v>617</v>
       </c>
@@ -23940,7 +23940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>618</v>
       </c>
@@ -23975,7 +23975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>619</v>
       </c>
@@ -24010,7 +24010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>620</v>
       </c>
@@ -24045,7 +24045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>621</v>
       </c>
@@ -24080,7 +24080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1">
         <v>622</v>
       </c>
@@ -24112,7 +24112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>623</v>
       </c>
@@ -24147,7 +24147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>624</v>
       </c>
@@ -24182,7 +24182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>625</v>
       </c>
@@ -24217,7 +24217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>626</v>
       </c>
@@ -24252,7 +24252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1">
         <v>627</v>
       </c>
@@ -24284,7 +24284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>628</v>
       </c>
@@ -24319,7 +24319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>629</v>
       </c>
@@ -24354,7 +24354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>630</v>
       </c>
@@ -24389,7 +24389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>631</v>
       </c>
@@ -24424,7 +24424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1">
         <v>632</v>
       </c>
@@ -24456,7 +24456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>633</v>
       </c>
@@ -24491,7 +24491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>634</v>
       </c>
@@ -24526,7 +24526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>635</v>
       </c>
@@ -24561,7 +24561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>636</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1">
         <v>637</v>
       </c>
@@ -24628,7 +24628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>638</v>
       </c>
@@ -24663,7 +24663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>639</v>
       </c>
@@ -24698,7 +24698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>640</v>
       </c>
@@ -24733,7 +24733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>641</v>
       </c>
@@ -24768,7 +24768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1">
         <v>642</v>
       </c>
@@ -24800,7 +24800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>643</v>
       </c>
@@ -24835,7 +24835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>644</v>
       </c>
@@ -24870,7 +24870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>645</v>
       </c>
@@ -24905,7 +24905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>646</v>
       </c>
@@ -24940,7 +24940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1">
         <v>647</v>
       </c>
@@ -24972,7 +24972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>648</v>
       </c>
@@ -25007,7 +25007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>649</v>
       </c>
@@ -25042,7 +25042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>650</v>
       </c>
@@ -25077,7 +25077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>651</v>
       </c>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="653" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
         <v>652</v>
       </c>
@@ -25144,7 +25144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>653</v>
       </c>
@@ -25179,7 +25179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>654</v>
       </c>
@@ -25214,7 +25214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>655</v>
       </c>
@@ -25249,7 +25249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>656</v>
       </c>
@@ -25284,7 +25284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="658" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1">
         <v>657</v>
       </c>
@@ -25316,7 +25316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>658</v>
       </c>
@@ -25351,7 +25351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>659</v>
       </c>
@@ -25386,7 +25386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>660</v>
       </c>
@@ -25421,7 +25421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>661</v>
       </c>
@@ -25456,7 +25456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1">
         <v>662</v>
       </c>
@@ -25488,7 +25488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>663</v>
       </c>
@@ -25523,7 +25523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>664</v>
       </c>
@@ -25558,7 +25558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>665</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>666</v>
       </c>
@@ -25628,7 +25628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
         <v>667</v>
       </c>
@@ -25660,7 +25660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>668</v>
       </c>
@@ -25695,7 +25695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>669</v>
       </c>
@@ -25730,7 +25730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>670</v>
       </c>
@@ -25765,7 +25765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>671</v>
       </c>
@@ -25800,7 +25800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="673" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1">
         <v>672</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>673</v>
       </c>
@@ -25867,7 +25867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>674</v>
       </c>
@@ -25902,7 +25902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>675</v>
       </c>
@@ -25937,7 +25937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>676</v>
       </c>
@@ -25972,7 +25972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
         <v>677</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>678</v>
       </c>
@@ -26039,7 +26039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>679</v>
       </c>
@@ -26074,7 +26074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>680</v>
       </c>
@@ -26109,7 +26109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>681</v>
       </c>
@@ -26144,7 +26144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
         <v>682</v>
       </c>
@@ -26176,7 +26176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>683</v>
       </c>
@@ -26211,7 +26211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>684</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>685</v>
       </c>
@@ -26281,7 +26281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>686</v>
       </c>
@@ -26316,7 +26316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="1">
         <v>687</v>
       </c>
@@ -26348,7 +26348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>688</v>
       </c>
@@ -26383,7 +26383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>689</v>
       </c>
@@ -26418,7 +26418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>690</v>
       </c>
@@ -26453,7 +26453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>691</v>
       </c>
@@ -26488,7 +26488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
         <v>692</v>
       </c>
@@ -26520,7 +26520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>693</v>
       </c>
@@ -26555,7 +26555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>694</v>
       </c>
@@ -26590,7 +26590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>695</v>
       </c>
@@ -26625,7 +26625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>696</v>
       </c>
@@ -26660,7 +26660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
         <v>697</v>
       </c>
@@ -26692,7 +26692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>698</v>
       </c>
@@ -26727,7 +26727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>699</v>
       </c>
@@ -26762,7 +26762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>700</v>
       </c>
@@ -26797,7 +26797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>701</v>
       </c>
@@ -26832,7 +26832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="1">
         <v>702</v>
       </c>
@@ -26864,7 +26864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>703</v>
       </c>
@@ -26899,7 +26899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>704</v>
       </c>
@@ -26934,7 +26934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>705</v>
       </c>
@@ -26969,7 +26969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>706</v>
       </c>
@@ -27004,7 +27004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="708" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="1">
         <v>707</v>
       </c>
@@ -27036,7 +27036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>708</v>
       </c>
@@ -27071,7 +27071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>709</v>
       </c>
@@ -27106,7 +27106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>710</v>
       </c>
@@ -27141,7 +27141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>711</v>
       </c>
@@ -27178,6 +27178,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 BV_C2_Internal</oddFooter>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -27185,6 +27188,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6385d03-c98b-47a8-b084-660309c480c9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1dad954f-e29e-48a7-b9b8-f0523de1045f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B05075DB2EB95E4AB0084D2AB051A38A" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1acf5709253336bc12ea482482f5d520">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6385d03-c98b-47a8-b084-660309c480c9" xmlns:ns3="1dad954f-e29e-48a7-b9b8-f0523de1045f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84ff94f6b93240dc82e76730a418228e" ns2:_="" ns3:_="">
     <xsd:import namespace="c6385d03-c98b-47a8-b084-660309c480c9"/>
@@ -27373,34 +27396,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6385d03-c98b-47a8-b084-660309c480c9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1dad954f-e29e-48a7-b9b8-f0523de1045f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4459DD-733E-45E1-8B5B-AB53FD8E0BD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9750802A-7E49-4C9E-A188-D2B89FA16918}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c6385d03-c98b-47a8-b084-660309c480c9"/>
+    <ds:schemaRef ds:uri="1dad954f-e29e-48a7-b9b8-f0523de1045f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09719356-4137-4EAA-8D91-69CF407697D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09719356-4137-4EAA-8D91-69CF407697D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9750802A-7E49-4C9E-A188-D2B89FA16918}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4459DD-733E-45E1-8B5B-AB53FD8E0BD9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c6385d03-c98b-47a8-b084-660309c480c9"/>
+    <ds:schemaRef ds:uri="1dad954f-e29e-48a7-b9b8-f0523de1045f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>